--- a/docs/AMA-website-content-template.xlsx
+++ b/docs/AMA-website-content-template.xlsx
@@ -877,7 +877,7 @@
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
     <col width="43" customWidth="1" min="2" max="2"/>
-    <col width="67" customWidth="1" min="3" max="3"/>
+    <col width="70" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -905,7 +905,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>60</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -920,14 +920,10 @@
           <t>dues_max</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Upper end of the dues range; leave blank once the amount is final</t>
+          <t>Upper end of a dues range, if the amount is ever a range; otherwise leave blank</t>
         </is>
       </c>
     </row>
